--- a/artfynd/S 997-2026 artfynd.xlsx
+++ b/artfynd/S 997-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74470045</v>
+        <v>136558542</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>57616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>52 Sandvik 1100 m SV, Sm</t>
+          <t>Norrbo campingplats, Madkroken, Nottebäck, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508857</v>
+        <v>508301</v>
       </c>
       <c r="R2" t="n">
-        <v>6327966</v>
+        <v>6327902</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F6c 0000. SOM: Goodyera repens. LEG: Kerstin Petersson</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,74 +773,81 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74470045</t>
+          <t>https://artportalen.se/Sighting/136558542</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74149734</v>
+        <v>136558512</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>58594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>102987</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L20 Lindesborg 1200 m N, Sm</t>
+          <t>Norrbo campingplats, Madkroken, Nottebäck, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511781</v>
+        <v>508301</v>
       </c>
       <c r="R3" t="n">
-        <v>6325801</v>
+        <v>6327902</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,17 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F5c 2829. SOM: Dactylorhiza maculata ssp. maculata. LEG: Kerstin Petersson, Alva Gustafsson</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,78 +887,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vattenfyllt djupt vägdike</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74149734</t>
+          <t>https://artportalen.se/Sighting/136558512</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117100204</v>
+        <v>74470045</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hjältingsåker, Sm</t>
+          <t>52 Sandvik 1100 m SV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507843</v>
+        <v>508857</v>
       </c>
       <c r="R4" t="n">
-        <v>6324057</v>
+        <v>6327966</v>
       </c>
       <c r="S4" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppvidinge</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -968,27 +968,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sjösås</t>
+          <t>Nottebäck</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>1991-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F6c 0000. SOM: Goodyera repens. LEG: Kerstin Petersson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,80 +994,74 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117100204</t>
+          <t>https://artportalen.se/Sighting/74470045</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127345855</v>
+        <v>74149734</v>
       </c>
       <c r="B5" t="n">
-        <v>92147</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karlslund, Sm</t>
+          <t>L20 Lindesborg 1200 m N, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510523</v>
+        <v>511781</v>
       </c>
       <c r="R5" t="n">
-        <v>6326521</v>
+        <v>6325801</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>1993-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F5c 2829. SOM: Dactylorhiza maculata ssp. maculata. LEG: Kerstin Petersson, Alva Gustafsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,59 +1104,42 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lärkplantage 25-årig</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Gammal granstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Gammal granstubbe</t>
+          <t>Vattenfyllt djupt vägdike</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127345855</t>
+          <t>https://artportalen.se/Sighting/74149734</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59225019</v>
+        <v>117100204</v>
       </c>
       <c r="B6" t="n">
-        <v>92632</v>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,37 +1147,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nottebäck, vägkryss söder om, Sm</t>
+          <t>Hjältingsåker, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511113</v>
+        <v>507843</v>
       </c>
       <c r="R6" t="n">
-        <v>6327127</v>
+        <v>6324057</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1186,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Uppvidinge</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1219,17 +1196,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Nottebäck</t>
+          <t>Sjösås</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-09-12</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-09-12</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,92 +1227,80 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>rötad innuti # gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59225019</t>
+          <t>https://artportalen.se/Sighting/117100204</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88638299</v>
+        <v>127345855</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>92147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hattehallvägen,Uppvidinge, Sm</t>
+          <t>Karlslund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510659</v>
+        <v>510523</v>
       </c>
       <c r="R7" t="n">
-        <v>6326606</v>
+        <v>6326521</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,22 +1324,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,33 +1338,59 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lärkplantage 25-årig</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Gammal granstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Gammal granstubbe</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Hultquist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Hultquist</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88638299</t>
+          <t>https://artportalen.se/Sighting/127345855</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102732875</v>
+        <v>59225019</v>
       </c>
       <c r="B8" t="n">
-        <v>57890</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,49 +1398,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100082</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nottebäckskrysset, Sm</t>
+          <t>Nottebäck, vägkryss söder om, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511367</v>
+        <v>511113</v>
       </c>
       <c r="R8" t="n">
-        <v>6327381</v>
+        <v>6327127</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,12 +1452,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2011-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2011-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,31 +1468,46 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>rötad innuti # gran</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Annchristin Nyström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Annchristin Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102732875</t>
+          <t>https://artportalen.se/Sighting/59225019</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119970716</v>
+        <v>88638299</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,37 +1515,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högaberg, Högaberg, Sm</t>
+          <t>Hattehallvägen,Uppvidinge, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510144</v>
+        <v>510659</v>
       </c>
       <c r="R9" t="n">
-        <v>6324573</v>
+        <v>6326606</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,22 +1577,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,27 +1607,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Thomas Hultquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Thomas Hultquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119970716</t>
+          <t>https://artportalen.se/Sighting/88638299</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125645935</v>
+        <v>102732875</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,37 +1635,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100082</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långemosse, Långemosse, Sm</t>
+          <t>Nottebäckskrysset, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509352</v>
+        <v>511367</v>
       </c>
       <c r="R10" t="n">
-        <v>6324443</v>
+        <v>6327381</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,22 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2022-08-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2022-08-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,27 +1721,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Mikael Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Mikael Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125645935</t>
+          <t>https://artportalen.se/Sighting/102732875</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94583857</v>
+        <v>119970716</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,42 +1749,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nottebäck krysset V Busshållsplats, Nottebäck, Sm</t>
+          <t>Högaberg, Högaberg, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511114</v>
+        <v>510144</v>
       </c>
       <c r="R11" t="n">
-        <v>6327182</v>
+        <v>6324573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,12 +1803,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,27 +1833,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94583857</t>
+          <t>https://artportalen.se/Sighting/119970716</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133177460</v>
+        <v>125645935</v>
       </c>
       <c r="B12" t="n">
-        <v>58461</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,53 +1861,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>O Karlslund, Nottebäck, Sm</t>
+          <t>Långemosse, Långemosse, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510646</v>
+        <v>509352</v>
       </c>
       <c r="R12" t="n">
-        <v>6326614</v>
+        <v>6324443</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,12 +1915,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,27 +1945,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Adam Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133177460</t>
+          <t>https://artportalen.se/Sighting/125645935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94583864</v>
+        <v>94583857</v>
       </c>
       <c r="B13" t="n">
-        <v>58085</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2066,16 +2066,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94583864</t>
+          <t>https://artportalen.se/Sighting/94583857</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2968514</v>
+        <v>133177460</v>
       </c>
       <c r="B14" t="n">
-        <v>99156</v>
+        <v>58461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,21 +2083,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2105,29 +2105,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitthult, Sm</t>
+          <t>O Karlslund, Nottebäck, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511613</v>
+        <v>510646</v>
       </c>
       <c r="R14" t="n">
-        <v>6325639</v>
+        <v>6326614</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,12 +2153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2003-07-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2003-07-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,36 +2169,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2968514</t>
+          <t>https://artportalen.se/Sighting/133177460</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2453677</v>
+        <v>94583864</v>
       </c>
       <c r="B15" t="n">
-        <v>99022</v>
+        <v>58085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,51 +2201,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>205976</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Galtabäck, Sm</t>
+          <t>Nottebäck krysset V Busshållsplats, Nottebäck, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509576</v>
+        <v>511114</v>
       </c>
       <c r="R15" t="n">
-        <v>6323736</v>
+        <v>6327182</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,12 +2263,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2001-06-16</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2001-06-16</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,36 +2279,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Skogskärr</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2453677</t>
+          <t>https://artportalen.se/Sighting/94583864</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117614853</v>
+        <v>2968514</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>99156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,21 +2311,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>219875</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2347,32 +2333,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnakärret, Sm</t>
+          <t>Vitthult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508742</v>
+        <v>511613</v>
       </c>
       <c r="R16" t="n">
-        <v>6322987</v>
+        <v>6325639</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2384,7 +2364,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppvidinge</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2394,32 +2374,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Sjösås</t>
+          <t>Nottebäck</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2003-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>2003-07-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,31 +2395,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil Johannesson</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Johannesson</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117614853</t>
+          <t>https://artportalen.se/Sighting/2968514</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117363855</v>
+        <v>2453677</v>
       </c>
       <c r="B17" t="n">
-        <v>57141</v>
+        <v>99022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,37 +2432,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grisakällan, Sm</t>
+          <t>Galtabäck, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508157</v>
+        <v>509576</v>
       </c>
       <c r="R17" t="n">
-        <v>6322327</v>
+        <v>6323736</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,7 +2485,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppvidinge</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2511,17 +2495,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Sjösås</t>
+          <t>Nottebäck</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2001-06-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2001-06-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,28 +2516,33 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Skogskärr</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117363855</t>
+          <t>https://artportalen.se/Sighting/2453677</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117624721</v>
+        <v>117614853</v>
       </c>
       <c r="B18" t="n">
         <v>57141</v>
@@ -2581,7 +2570,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2589,9 +2582,10 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2599,17 +2593,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mästreda, Mästreda, Sm</t>
+          <t>Kvarnakärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508045</v>
+        <v>508742</v>
       </c>
       <c r="R18" t="n">
-        <v>6321881</v>
+        <v>6322987</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2633,27 +2627,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Höna med 4 kycklingar</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,24 +2662,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Emil Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Adam Johannesson</t>
+          <t>Emil Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117624721</t>
+          <t>https://artportalen.se/Sighting/117614853</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117363747</v>
+        <v>117363855</v>
       </c>
       <c r="B19" t="n">
         <v>57141</v>
@@ -2714,21 +2708,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandsjöryd, Sm</t>
+          <t>Grisakällan, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508258</v>
+        <v>508157</v>
       </c>
       <c r="R19" t="n">
-        <v>6321633</v>
+        <v>6322327</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2785,6 +2774,245 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117363855</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117624721</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mästreda, Mästreda, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>508045</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6321881</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sjösås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Höna med 4 kycklingar</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Adam Johannesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Adam Johannesson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117624721</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117363747</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sandsjöryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>508258</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6321633</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sjösås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Adam Johannesson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Adam Johannesson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/117363747</t>
         </is>
@@ -2810,6 +3038,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
